--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.68901</v>
+        <v>16.94493</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63959</v>
+        <v>16.71844</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45344</v>
+        <v>16.77649</v>
       </c>
       <c r="F2" t="n">
-        <v>43.83682</v>
+        <v>42.28274</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05024</v>
+        <v>0.05012</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8376</v>
+        <v>1.84864</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.60405</v>
+        <v>17.0728</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75392</v>
+        <v>16.85262</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61587</v>
+        <v>17.03681</v>
       </c>
       <c r="F3" t="n">
-        <v>43.1647</v>
+        <v>43.45062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05083</v>
+        <v>0.05013</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8092</v>
+        <v>1.83348</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.03261</v>
+        <v>17.32923</v>
       </c>
       <c r="D4" t="n">
-        <v>16.89118</v>
+        <v>16.93584</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90011</v>
+        <v>16.96621</v>
       </c>
       <c r="F4" t="n">
-        <v>43.06597</v>
+        <v>43.29161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05075</v>
+        <v>0.05064</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86269</v>
+        <v>1.8289</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.19889</v>
+        <v>16.63848</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37639</v>
+        <v>16.39476</v>
       </c>
       <c r="E6" t="n">
-        <v>16.94118</v>
+        <v>16.44365</v>
       </c>
       <c r="F6" t="n">
-        <v>21.98167</v>
+        <v>21.57618</v>
       </c>
       <c r="G6" t="n">
-        <v>34.54212</v>
+        <v>33.90048</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.79746</v>
+        <v>16.60456</v>
       </c>
       <c r="D7" t="n">
-        <v>16.02522</v>
+        <v>16.37306</v>
       </c>
       <c r="E7" t="n">
-        <v>16.90777</v>
+        <v>16.45262</v>
       </c>
       <c r="F7" t="n">
-        <v>22.11467</v>
+        <v>22.10159</v>
       </c>
       <c r="G7" t="n">
-        <v>34.89914</v>
+        <v>34.32877</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.6969</v>
+        <v>17.00765</v>
       </c>
       <c r="D8" t="n">
-        <v>16.35462</v>
+        <v>16.12505</v>
       </c>
       <c r="E8" t="n">
-        <v>16.60295</v>
+        <v>16.57279</v>
       </c>
       <c r="F8" t="n">
-        <v>21.59877</v>
+        <v>22.01724</v>
       </c>
       <c r="G8" t="n">
-        <v>35.59536</v>
+        <v>34.5355</v>
       </c>
     </row>
   </sheetData>
